--- a/output/pdf_financials_xlsx/MKP.xlsx
+++ b/output/pdf_financials_xlsx/MKP.xlsx
@@ -650,11 +650,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="R4" s="3" t="n">
-        <v>96.40300000000001</v>
-      </c>
-      <c r="S4" s="3" t="n">
-        <v>95.839</v>
+      <c r="R4" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S4" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -840,15 +844,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="R6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="R6" s="3" t="n">
+        <v>96.40300000000001</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>95.839</v>
       </c>
     </row>
     <row r="7">
@@ -950,53 +950,85 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="3" t="n">
-        <v>0</v>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E8" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H8" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I8" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J8" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L8" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M8" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O8" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P8" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q8" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R8" s="3" t="n">
         <v>133.849</v>
@@ -1250,53 +1282,85 @@
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="3" t="n">
-        <v>0</v>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E12" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G12" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H12" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I12" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J12" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L12" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M12" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O12" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P12" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q12" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R12" s="3" t="n">
         <v>133.849</v>
@@ -1555,53 +1619,85 @@
           <t>Operating Income</t>
         </is>
       </c>
-      <c r="B17" s="3" t="n">
-        <v>-5.734</v>
-      </c>
-      <c r="C17" s="3" t="n">
-        <v>-5.899</v>
-      </c>
-      <c r="D17" s="3" t="n">
-        <v>-6.1</v>
-      </c>
-      <c r="E17" s="3" t="n">
-        <v>-6.86</v>
-      </c>
-      <c r="F17" s="3" t="n">
-        <v>-8.993</v>
-      </c>
-      <c r="G17" s="3" t="n">
-        <v>-11.29</v>
-      </c>
-      <c r="H17" s="3" t="n">
-        <v>-13.383</v>
-      </c>
-      <c r="I17" s="3" t="n">
-        <v>-14.508</v>
-      </c>
-      <c r="J17" s="3" t="n">
-        <v>-17.963</v>
-      </c>
-      <c r="K17" s="3" t="n">
-        <v>-19.218</v>
-      </c>
-      <c r="L17" s="3" t="n">
-        <v>-18.922</v>
-      </c>
-      <c r="M17" s="3" t="n">
-        <v>-21.197</v>
-      </c>
-      <c r="N17" s="3" t="n">
-        <v>-21.678</v>
-      </c>
-      <c r="O17" s="3" t="n">
-        <v>-27.447</v>
-      </c>
-      <c r="P17" s="3" t="n">
-        <v>-28.637</v>
-      </c>
-      <c r="Q17" s="3" t="n">
-        <v>-33.572</v>
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C17" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E17" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F17" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G17" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H17" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I17" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J17" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K17" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L17" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M17" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N17" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O17" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P17" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q17" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R17" s="3" t="n">
         <v>79.812</v>
@@ -3137,95 +3233,59 @@
           <t>Money Market Investments</t>
         </is>
       </c>
-      <c r="B41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -3683,11 +3743,15 @@
           <t xml:space="preserve">    Marketable Securities</t>
         </is>
       </c>
-      <c r="B47" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C47" s="3" t="n">
-        <v>0</v>
+      <c r="B47" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C47" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D47" s="3" t="n">
         <v>290.228</v>
@@ -3805,59 +3869,95 @@
           <t xml:space="preserve">    Accounts Receivable</t>
         </is>
       </c>
-      <c r="B49" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C49" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D49" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E49" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F49" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G49" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M49" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N49" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O49" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q49" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R49" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S49" s="3" t="n">
-        <v>0</v>
+      <c r="B49" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C49" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D49" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E49" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F49" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G49" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H49" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I49" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J49" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K49" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L49" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M49" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N49" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O49" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P49" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q49" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R49" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S49" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="50">
@@ -3866,59 +3966,95 @@
           <t xml:space="preserve">    Notes Receivable</t>
         </is>
       </c>
-      <c r="B50" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C50" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D50" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E50" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F50" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G50" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K50" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M50" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O50" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q50" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R50" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S50" s="3" t="n">
-        <v>0</v>
+      <c r="B50" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C50" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D50" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E50" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F50" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G50" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H50" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I50" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J50" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K50" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L50" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M50" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N50" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O50" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P50" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q50" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R50" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S50" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="51">
@@ -3927,59 +4063,95 @@
           <t xml:space="preserve">    Loans Receivable</t>
         </is>
       </c>
-      <c r="B51" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C51" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D51" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E51" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F51" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G51" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O51" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q51" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R51" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S51" s="3" t="n">
-        <v>0</v>
+      <c r="B51" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C51" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D51" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E51" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F51" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G51" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H51" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I51" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J51" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K51" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L51" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M51" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N51" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O51" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P51" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q51" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R51" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S51" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="52">
@@ -3988,59 +4160,95 @@
           <t xml:space="preserve">    Other Current Receivables</t>
         </is>
       </c>
-      <c r="B52" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C52" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D52" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E52" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F52" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G52" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H52" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K52" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L52" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M52" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N52" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O52" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P52" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q52" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R52" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S52" s="3" t="n">
-        <v>0</v>
+      <c r="B52" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C52" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D52" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E52" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F52" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G52" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H52" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I52" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J52" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K52" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L52" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M52" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N52" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O52" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P52" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q52" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R52" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S52" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="53">
@@ -4049,59 +4257,95 @@
           <t xml:space="preserve">  Total Receivables</t>
         </is>
       </c>
-      <c r="B53" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C53" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D53" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E53" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F53" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G53" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L53" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M53" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O53" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q53" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R53" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S53" s="3" t="n">
-        <v>0</v>
+      <c r="B53" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C53" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D53" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E53" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F53" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G53" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H53" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I53" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J53" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K53" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L53" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M53" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N53" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O53" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P53" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q53" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R53" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S53" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="54">
@@ -4110,59 +4354,95 @@
           <t xml:space="preserve">    Inventories, Raw Materials &amp; Components</t>
         </is>
       </c>
-      <c r="B54" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C54" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D54" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E54" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F54" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G54" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O54" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q54" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R54" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S54" s="3" t="n">
-        <v>0</v>
+      <c r="B54" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C54" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D54" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E54" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F54" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G54" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H54" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I54" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J54" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K54" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L54" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M54" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N54" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O54" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P54" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q54" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R54" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S54" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="55">
@@ -4171,59 +4451,95 @@
           <t xml:space="preserve">    Inventories, Work In Process</t>
         </is>
       </c>
-      <c r="B55" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C55" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D55" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E55" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F55" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G55" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I55" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M55" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N55" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O55" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q55" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R55" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S55" s="3" t="n">
-        <v>0</v>
+      <c r="B55" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C55" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D55" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E55" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F55" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G55" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H55" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I55" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J55" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K55" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L55" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M55" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N55" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O55" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P55" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q55" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R55" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S55" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="56">
@@ -4232,59 +4548,95 @@
           <t xml:space="preserve">    Inventories, Inventories Adjustments</t>
         </is>
       </c>
-      <c r="B56" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C56" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D56" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E56" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F56" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G56" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H56" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M56" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N56" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O56" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q56" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R56" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S56" s="3" t="n">
-        <v>0</v>
+      <c r="B56" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C56" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D56" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E56" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F56" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G56" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H56" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I56" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J56" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K56" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L56" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M56" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N56" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O56" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P56" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q56" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R56" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S56" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="57">
@@ -4293,59 +4645,95 @@
           <t xml:space="preserve">    Inventories, Finished Goods</t>
         </is>
       </c>
-      <c r="B57" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C57" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D57" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E57" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F57" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G57" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H57" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J57" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K57" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M57" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N57" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O57" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P57" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q57" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R57" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S57" s="3" t="n">
-        <v>0</v>
+      <c r="B57" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C57" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D57" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E57" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F57" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G57" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H57" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I57" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J57" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K57" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L57" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M57" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N57" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O57" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P57" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q57" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R57" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S57" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="58">
@@ -4354,59 +4742,95 @@
           <t xml:space="preserve">    Inventories, Other</t>
         </is>
       </c>
-      <c r="B58" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C58" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D58" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E58" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F58" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G58" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H58" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K58" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M58" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N58" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O58" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P58" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R58" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S58" s="3" t="n">
-        <v>0</v>
+      <c r="B58" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C58" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D58" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E58" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F58" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G58" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H58" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I58" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J58" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K58" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L58" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M58" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N58" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O58" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P58" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q58" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R58" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S58" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="59">
@@ -4415,59 +4839,95 @@
           <t xml:space="preserve">  Total Inventories</t>
         </is>
       </c>
-      <c r="B59" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C59" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D59" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E59" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F59" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G59" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H59" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K59" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L59" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M59" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N59" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O59" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P59" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q59" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R59" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S59" s="3" t="n">
-        <v>0</v>
+      <c r="B59" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C59" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D59" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E59" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F59" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G59" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H59" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I59" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J59" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K59" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L59" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M59" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N59" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O59" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P59" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q59" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R59" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S59" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="60">
@@ -4476,59 +4936,95 @@
           <t xml:space="preserve">  Other Current Assets</t>
         </is>
       </c>
-      <c r="B60" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C60" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D60" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E60" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F60" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G60" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H60" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K60" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M60" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N60" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O60" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P60" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q60" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R60" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S60" s="3" t="n">
-        <v>0</v>
+      <c r="B60" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C60" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D60" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E60" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F60" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G60" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H60" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I60" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J60" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K60" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L60" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M60" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N60" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O60" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P60" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q60" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R60" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S60" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="61">
@@ -4634,59 +5130,95 @@
           <t xml:space="preserve">  Investments And Advances</t>
         </is>
       </c>
-      <c r="B62" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C62" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D62" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E62" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F62" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G62" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H62" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I62" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K62" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M62" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N62" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O62" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P62" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q62" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R62" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S62" s="3" t="n">
-        <v>0</v>
+      <c r="B62" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C62" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D62" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E62" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F62" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G62" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H62" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I62" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J62" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K62" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L62" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M62" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N62" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O62" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P62" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q62" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R62" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S62" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="63">
@@ -4695,59 +5227,95 @@
           <t xml:space="preserve">      Land And Improvements</t>
         </is>
       </c>
-      <c r="B63" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C63" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D63" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E63" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F63" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G63" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H63" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I63" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K63" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L63" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M63" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N63" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O63" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P63" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q63" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R63" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S63" s="3" t="n">
-        <v>0</v>
+      <c r="B63" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C63" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D63" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E63" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F63" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G63" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H63" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I63" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J63" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K63" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L63" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M63" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N63" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O63" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P63" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q63" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R63" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S63" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="64">
@@ -4756,59 +5324,95 @@
           <t xml:space="preserve">      Buildings And Improvements</t>
         </is>
       </c>
-      <c r="B64" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C64" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D64" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E64" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F64" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G64" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H64" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I64" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K64" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L64" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M64" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N64" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O64" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P64" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q64" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R64" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S64" s="3" t="n">
-        <v>0</v>
+      <c r="B64" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C64" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D64" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E64" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F64" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G64" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H64" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I64" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J64" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K64" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L64" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M64" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N64" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O64" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P64" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q64" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R64" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S64" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="65">
@@ -4817,59 +5421,95 @@
           <t xml:space="preserve">      Machinery, Furniture, Equipment</t>
         </is>
       </c>
-      <c r="B65" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C65" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D65" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E65" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F65" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G65" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H65" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I65" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K65" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L65" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M65" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N65" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O65" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P65" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q65" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R65" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S65" s="3" t="n">
-        <v>0</v>
+      <c r="B65" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C65" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D65" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E65" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F65" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G65" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H65" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I65" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J65" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K65" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L65" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M65" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N65" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O65" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P65" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q65" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R65" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S65" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="66">
@@ -4878,59 +5518,95 @@
           <t xml:space="preserve">      Construction In Progress</t>
         </is>
       </c>
-      <c r="B66" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C66" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D66" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E66" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F66" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G66" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H66" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I66" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K66" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M66" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N66" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O66" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P66" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q66" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R66" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S66" s="3" t="n">
-        <v>0</v>
+      <c r="B66" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C66" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D66" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E66" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F66" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G66" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H66" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I66" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J66" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K66" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L66" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M66" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N66" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O66" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P66" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q66" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R66" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S66" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="67">
@@ -5036,59 +5712,95 @@
           <t xml:space="preserve">    Gross Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B68" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C68" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D68" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E68" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F68" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G68" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H68" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I68" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J68" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K68" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L68" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M68" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N68" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O68" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P68" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q68" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R68" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S68" s="3" t="n">
-        <v>0</v>
+      <c r="B68" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C68" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D68" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E68" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F68" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G68" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H68" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I68" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J68" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K68" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L68" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M68" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N68" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O68" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P68" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q68" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R68" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S68" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="69">
@@ -5097,59 +5809,95 @@
           <t xml:space="preserve">    Accumulated Depreciation</t>
         </is>
       </c>
-      <c r="B69" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C69" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D69" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E69" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F69" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G69" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H69" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I69" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J69" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K69" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L69" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M69" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N69" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O69" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P69" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q69" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R69" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S69" s="3" t="n">
-        <v>0</v>
+      <c r="B69" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C69" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D69" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E69" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F69" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G69" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H69" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I69" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J69" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K69" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L69" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M69" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N69" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O69" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P69" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q69" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R69" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S69" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="70">
@@ -5158,59 +5906,95 @@
           <t xml:space="preserve">  Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B70" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C70" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D70" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E70" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F70" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G70" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H70" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I70" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J70" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K70" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L70" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M70" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N70" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O70" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P70" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q70" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R70" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S70" s="3" t="n">
-        <v>0</v>
+      <c r="B70" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C70" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D70" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E70" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F70" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G70" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H70" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I70" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J70" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K70" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L70" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M70" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N70" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O70" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P70" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q70" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R70" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S70" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="71">
@@ -5219,59 +6003,95 @@
           <t xml:space="preserve">  Intangible Assets</t>
         </is>
       </c>
-      <c r="B71" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C71" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D71" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E71" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F71" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G71" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H71" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I71" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K71" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L71" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M71" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N71" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O71" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P71" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q71" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R71" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S71" s="3" t="n">
-        <v>0</v>
+      <c r="B71" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C71" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D71" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E71" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F71" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G71" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H71" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I71" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J71" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K71" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L71" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M71" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N71" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O71" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P71" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q71" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R71" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S71" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="72">
@@ -5280,59 +6100,95 @@
           <t xml:space="preserve">    Goodwill</t>
         </is>
       </c>
-      <c r="B72" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C72" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D72" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E72" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F72" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G72" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H72" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J72" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K72" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L72" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M72" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N72" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O72" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P72" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q72" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R72" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S72" s="3" t="n">
-        <v>0</v>
+      <c r="B72" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C72" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D72" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E72" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F72" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G72" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H72" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I72" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J72" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K72" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L72" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M72" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N72" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O72" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P72" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q72" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R72" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S72" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="73">
@@ -5341,59 +6197,95 @@
           <t xml:space="preserve">  Other Long Term Assets</t>
         </is>
       </c>
-      <c r="B73" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C73" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D73" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E73" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F73" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G73" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H73" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I73" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K73" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L73" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M73" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N73" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O73" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P73" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q73" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R73" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S73" s="3" t="n">
-        <v>0</v>
+      <c r="B73" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C73" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D73" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E73" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F73" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G73" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H73" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I73" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J73" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K73" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L73" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M73" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N73" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O73" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P73" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q73" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R73" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S73" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="74">
@@ -5560,59 +6452,95 @@
           <t xml:space="preserve">    Accounts Payable</t>
         </is>
       </c>
-      <c r="B76" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C76" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D76" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E76" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F76" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G76" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H76" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I76" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J76" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K76" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L76" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M76" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N76" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O76" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P76" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q76" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R76" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S76" s="3" t="n">
-        <v>0</v>
+      <c r="B76" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C76" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D76" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E76" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F76" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G76" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H76" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I76" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J76" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K76" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L76" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M76" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N76" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O76" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P76" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q76" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R76" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S76" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="77">
@@ -5621,59 +6549,95 @@
           <t xml:space="preserve">    Total Tax Payable</t>
         </is>
       </c>
-      <c r="B77" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C77" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D77" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E77" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F77" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G77" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H77" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I77" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J77" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K77" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L77" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M77" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N77" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O77" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P77" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q77" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R77" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S77" s="3" t="n">
-        <v>0</v>
+      <c r="B77" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C77" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D77" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E77" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F77" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G77" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H77" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I77" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J77" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K77" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L77" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M77" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N77" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O77" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P77" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q77" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R77" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S77" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="78">
@@ -5682,59 +6646,95 @@
           <t xml:space="preserve">    Other Current Payables</t>
         </is>
       </c>
-      <c r="B78" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C78" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D78" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E78" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F78" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G78" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H78" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I78" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J78" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K78" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L78" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M78" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N78" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O78" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P78" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q78" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R78" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S78" s="3" t="n">
-        <v>0</v>
+      <c r="B78" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C78" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D78" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E78" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F78" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G78" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H78" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I78" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J78" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K78" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L78" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M78" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N78" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O78" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P78" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q78" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R78" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S78" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="79">
@@ -5743,59 +6743,95 @@
           <t xml:space="preserve">    Current Accrued Expense</t>
         </is>
       </c>
-      <c r="B79" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C79" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D79" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E79" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F79" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G79" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H79" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I79" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J79" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K79" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L79" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M79" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N79" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O79" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P79" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q79" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R79" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S79" s="3" t="n">
-        <v>0</v>
+      <c r="B79" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C79" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D79" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E79" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F79" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G79" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H79" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I79" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J79" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K79" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L79" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M79" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N79" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O79" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P79" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q79" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R79" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S79" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="80">
@@ -5804,59 +6840,95 @@
           <t xml:space="preserve">  Accounts Payable &amp; Accrued Expense</t>
         </is>
       </c>
-      <c r="B80" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C80" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D80" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E80" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F80" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G80" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H80" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I80" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J80" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K80" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L80" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M80" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N80" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O80" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P80" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q80" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R80" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S80" s="3" t="n">
-        <v>0</v>
+      <c r="B80" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C80" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D80" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E80" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F80" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G80" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H80" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I80" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J80" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K80" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L80" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M80" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N80" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O80" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P80" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q80" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R80" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S80" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="81">
@@ -5865,44 +6937,66 @@
           <t xml:space="preserve">    Short-Term Debt</t>
         </is>
       </c>
-      <c r="B81" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C81" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D81" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E81" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F81" s="3" t="n">
-        <v>0</v>
+      <c r="B81" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C81" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D81" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E81" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F81" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G81" s="3" t="n">
         <v>17.991</v>
       </c>
-      <c r="H81" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I81" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J81" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K81" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L81" s="3" t="n">
-        <v>0</v>
+      <c r="H81" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I81" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J81" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K81" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L81" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M81" s="3" t="n">
         <v>5.053</v>
       </c>
-      <c r="N81" s="3" t="n">
-        <v>0</v>
+      <c r="N81" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O81" s="3" t="n">
         <v>57.34</v>
@@ -5926,59 +7020,95 @@
           <t xml:space="preserve">    Short-Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B82" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C82" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D82" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E82" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F82" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G82" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H82" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I82" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J82" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K82" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L82" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M82" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N82" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O82" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P82" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q82" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R82" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S82" s="3" t="n">
-        <v>0</v>
+      <c r="B82" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C82" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D82" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E82" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F82" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G82" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H82" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I82" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J82" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K82" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L82" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M82" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N82" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O82" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P82" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q82" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R82" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S82" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="83">
@@ -5987,44 +7117,66 @@
           <t xml:space="preserve">  Short-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B83" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C83" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D83" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E83" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F83" s="3" t="n">
-        <v>0</v>
+      <c r="B83" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C83" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D83" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E83" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F83" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G83" s="3" t="n">
         <v>17.991</v>
       </c>
-      <c r="H83" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K83" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L83" s="3" t="n">
-        <v>0</v>
+      <c r="H83" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I83" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J83" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L83" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M83" s="3" t="n">
         <v>5.053</v>
       </c>
-      <c r="N83" s="3" t="n">
-        <v>0</v>
+      <c r="N83" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O83" s="3" t="n">
         <v>57.34</v>
@@ -6048,59 +7200,95 @@
           <t xml:space="preserve">    Current Deferred Revenue</t>
         </is>
       </c>
-      <c r="B84" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C84" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D84" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E84" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F84" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G84" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H84" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I84" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J84" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K84" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L84" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M84" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N84" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O84" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P84" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q84" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R84" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S84" s="3" t="n">
-        <v>0</v>
+      <c r="B84" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C84" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D84" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E84" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F84" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G84" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H84" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I84" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J84" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K84" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L84" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M84" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N84" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O84" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P84" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q84" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R84" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S84" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="85">
@@ -6109,59 +7297,95 @@
           <t xml:space="preserve">    Current Deferred Taxes Liabilities</t>
         </is>
       </c>
-      <c r="B85" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C85" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D85" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E85" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F85" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G85" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H85" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I85" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J85" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K85" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L85" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M85" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N85" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O85" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P85" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q85" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R85" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S85" s="3" t="n">
-        <v>0</v>
+      <c r="B85" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C85" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D85" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E85" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F85" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G85" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H85" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I85" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J85" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L85" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M85" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N85" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O85" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P85" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q85" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R85" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S85" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="86">
@@ -6170,59 +7394,95 @@
           <t xml:space="preserve">  Deferred Tax And Revenue</t>
         </is>
       </c>
-      <c r="B86" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C86" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D86" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E86" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F86" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G86" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H86" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I86" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J86" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K86" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L86" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M86" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N86" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O86" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P86" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q86" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R86" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S86" s="3" t="n">
-        <v>0</v>
+      <c r="B86" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C86" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D86" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E86" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F86" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G86" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H86" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I86" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J86" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K86" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L86" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M86" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N86" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O86" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P86" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q86" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R86" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S86" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="87">
@@ -6231,11 +7491,15 @@
           <t xml:space="preserve">  Other Current Liabilities</t>
         </is>
       </c>
-      <c r="B87" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C87" s="3" t="n">
-        <v>0</v>
+      <c r="B87" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C87" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D87" s="3" t="n">
         <v>2.248</v>
@@ -6243,47 +7507,75 @@
       <c r="E87" s="3" t="n">
         <v>5.728</v>
       </c>
-      <c r="F87" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G87" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H87" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I87" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J87" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K87" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L87" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M87" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N87" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O87" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P87" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q87" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R87" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S87" s="3" t="n">
-        <v>0</v>
+      <c r="F87" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G87" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H87" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I87" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J87" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K87" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L87" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M87" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N87" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O87" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P87" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q87" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R87" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S87" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="88">
@@ -6385,59 +7677,95 @@
           <t xml:space="preserve">    Long-Term Debt</t>
         </is>
       </c>
-      <c r="B89" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C89" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D89" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E89" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F89" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G89" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H89" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I89" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J89" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K89" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L89" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M89" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N89" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O89" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P89" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q89" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R89" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S89" s="3" t="n">
-        <v>0</v>
+      <c r="B89" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C89" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D89" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E89" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F89" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G89" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H89" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I89" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J89" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K89" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L89" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M89" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N89" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O89" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P89" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q89" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R89" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S89" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="90">
@@ -6446,59 +7774,95 @@
           <t xml:space="preserve">    Long-Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B90" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C90" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D90" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E90" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F90" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G90" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H90" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I90" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J90" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K90" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L90" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M90" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N90" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O90" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P90" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q90" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R90" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S90" s="3" t="n">
-        <v>0</v>
+      <c r="B90" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C90" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D90" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E90" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F90" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G90" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H90" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I90" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J90" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K90" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L90" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M90" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N90" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O90" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P90" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q90" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R90" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S90" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="91">
@@ -6507,59 +7871,95 @@
           <t xml:space="preserve">  Long-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B91" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C91" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D91" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K91" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L91" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M91" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N91" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O91" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P91" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q91" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R91" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S91" s="3" t="n">
-        <v>0</v>
+      <c r="B91" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C91" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D91" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E91" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F91" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G91" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H91" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I91" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J91" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L91" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M91" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N91" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O91" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P91" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q91" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R91" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S91" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="92">
@@ -6809,59 +8209,95 @@
           <t>Other Liabilities for Banks</t>
         </is>
       </c>
-      <c r="B95" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C95" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D95" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E95" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F95" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G95" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H95" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I95" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J95" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K95" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L95" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M95" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N95" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O95" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P95" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q95" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R95" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S95" s="3" t="n">
-        <v>0</v>
+      <c r="B95" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C95" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D95" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E95" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F95" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G95" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H95" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I95" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J95" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K95" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L95" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M95" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N95" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O95" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P95" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q95" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R95" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S95" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="96">
@@ -6870,59 +8306,95 @@
           <t xml:space="preserve">  Pension And Retirement Benefit</t>
         </is>
       </c>
-      <c r="B96" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C96" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D96" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K96" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M96" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N96" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O96" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q96" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R96" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S96" s="3" t="n">
-        <v>0</v>
+      <c r="B96" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C96" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D96" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E96" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F96" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G96" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H96" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I96" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J96" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K96" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L96" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M96" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N96" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O96" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P96" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q96" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R96" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S96" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="97">
@@ -6931,59 +8403,95 @@
           <t xml:space="preserve">    NonCurrent Deferred Revenue</t>
         </is>
       </c>
-      <c r="B97" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C97" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D97" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E97" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F97" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G97" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I97" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J97" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K97" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L97" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M97" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N97" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O97" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P97" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q97" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R97" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S97" s="3" t="n">
-        <v>0</v>
+      <c r="B97" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C97" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D97" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E97" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F97" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G97" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H97" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I97" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J97" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K97" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L97" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M97" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N97" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O97" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P97" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q97" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R97" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S97" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="98">
@@ -6992,11 +8500,15 @@
           <t xml:space="preserve">  NonCurrent Deferred Liabilities</t>
         </is>
       </c>
-      <c r="B98" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C98" s="3" t="n">
-        <v>0</v>
+      <c r="B98" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C98" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D98" s="3" t="n">
         <v>3.455</v>
@@ -7028,23 +8540,35 @@
       <c r="M98" s="3" t="n">
         <v>0.021</v>
       </c>
-      <c r="N98" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O98" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P98" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q98" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R98" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S98" s="3" t="n">
-        <v>0</v>
+      <c r="N98" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O98" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P98" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q98" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R98" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S98" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="99">
@@ -7053,11 +8577,15 @@
           <t xml:space="preserve">  NonCurrent Deferred Income Tax</t>
         </is>
       </c>
-      <c r="B99" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C99" s="3" t="n">
-        <v>0</v>
+      <c r="B99" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C99" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D99" s="3" t="n">
         <v>3.455</v>
@@ -7089,23 +8617,35 @@
       <c r="M99" s="3" t="n">
         <v>0.021</v>
       </c>
-      <c r="N99" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O99" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P99" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q99" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R99" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S99" s="3" t="n">
-        <v>0</v>
+      <c r="N99" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O99" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P99" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q99" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R99" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S99" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="100">
@@ -7114,11 +8654,15 @@
           <t xml:space="preserve">  Other Long-Term Liabilities</t>
         </is>
       </c>
-      <c r="B100" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C100" s="3" t="n">
-        <v>0</v>
+      <c r="B100" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C100" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D100" s="3" t="n">
         <v>368.048</v>
@@ -7126,47 +8670,75 @@
       <c r="E100" s="3" t="n">
         <v>427.693</v>
       </c>
-      <c r="F100" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G100" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K100" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L100" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M100" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N100" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O100" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P100" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q100" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R100" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S100" s="3" t="n">
-        <v>0</v>
+      <c r="F100" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G100" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H100" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I100" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J100" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K100" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L100" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M100" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N100" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O100" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P100" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q100" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R100" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S100" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="101">
@@ -7390,59 +8962,95 @@
           <t xml:space="preserve">  Preferred Stock</t>
         </is>
       </c>
-      <c r="B104" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C104" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D104" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E104" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F104" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G104" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H104" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I104" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J104" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K104" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L104" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M104" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N104" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O104" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P104" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q104" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R104" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S104" s="3" t="n">
-        <v>0</v>
+      <c r="B104" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C104" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D104" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E104" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F104" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G104" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H104" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I104" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J104" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K104" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L104" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M104" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N104" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O104" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P104" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q104" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R104" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S104" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="105">
@@ -7521,8 +9129,10 @@
       <c r="D106" s="3" t="n">
         <v>1.791</v>
       </c>
-      <c r="E106" s="3" t="n">
-        <v>0</v>
+      <c r="E106" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F106" s="3" t="n">
         <v>2.281</v>
@@ -7545,14 +9155,20 @@
       <c r="L106" s="3" t="n">
         <v>2141.072</v>
       </c>
-      <c r="M106" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N106" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O106" s="3" t="n">
-        <v>0</v>
+      <c r="M106" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N106" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O106" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P106" s="3" t="n">
         <v>-0.176</v>
@@ -7634,59 +9250,95 @@
           <t xml:space="preserve">  Treasury Stock</t>
         </is>
       </c>
-      <c r="B108" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C108" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D108" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E108" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F108" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G108" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H108" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I108" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J108" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K108" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L108" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M108" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N108" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O108" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P108" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q108" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R108" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S108" s="3" t="n">
-        <v>0</v>
+      <c r="B108" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C108" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D108" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E108" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F108" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G108" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H108" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I108" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J108" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K108" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L108" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M108" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N108" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O108" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P108" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q108" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R108" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S108" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="109">
@@ -7756,59 +9408,95 @@
           <t xml:space="preserve">  Minority Interest</t>
         </is>
       </c>
-      <c r="B110" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C110" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D110" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E110" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F110" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G110" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H110" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I110" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J110" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K110" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L110" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M110" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N110" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O110" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P110" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q110" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R110" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S110" s="3" t="n">
-        <v>0</v>
+      <c r="B110" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C110" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D110" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E110" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F110" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G110" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H110" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I110" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J110" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K110" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L110" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M110" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N110" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O110" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P110" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q110" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R110" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S110" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="111">
@@ -64559,7 +66247,7 @@
       </c>
       <c r="D528" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>NetInterestIncome</t>
         </is>
       </c>
       <c r="E528" t="inlineStr">

--- a/output/pdf_financials_xlsx/MKP.xlsx
+++ b/output/pdf_financials_xlsx/MKP.xlsx
@@ -844,11 +844,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="R6" s="3" t="n">
-        <v>96.40300000000001</v>
-      </c>
-      <c r="S6" s="3" t="n">
-        <v>95.839</v>
+      <c r="R6" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S6" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -950,85 +954,53 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="R8" s="3" t="n">
         <v>133.849</v>
@@ -1282,85 +1254,53 @@
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="R12" s="3" t="n">
         <v>133.849</v>
@@ -1619,85 +1559,53 @@
           <t>Operating Income</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B17" s="3" t="n">
+        <v>-5.734</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>-5.899</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>-6.1</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>-6.86</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>-8.993</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>-11.29</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>-13.383</v>
+      </c>
+      <c r="I17" s="3" t="n">
+        <v>-14.508</v>
+      </c>
+      <c r="J17" s="3" t="n">
+        <v>-17.963</v>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v>-19.218</v>
+      </c>
+      <c r="L17" s="3" t="n">
+        <v>-18.922</v>
+      </c>
+      <c r="M17" s="3" t="n">
+        <v>-21.197</v>
+      </c>
+      <c r="N17" s="3" t="n">
+        <v>-21.678</v>
+      </c>
+      <c r="O17" s="3" t="n">
+        <v>-27.447</v>
+      </c>
+      <c r="P17" s="3" t="n">
+        <v>-28.637</v>
+      </c>
+      <c r="Q17" s="3" t="n">
+        <v>-33.572</v>
       </c>
       <c r="R17" s="3" t="n">
         <v>79.812</v>
@@ -1761,10 +1669,10 @@
         <v>0</v>
       </c>
       <c r="R18" s="3" t="n">
-        <v>0</v>
+        <v>96.40300000000001</v>
       </c>
       <c r="S18" s="3" t="n">
-        <v>0</v>
+        <v>95.839</v>
       </c>
     </row>
     <row r="19">
@@ -2748,10 +2656,10 @@
         <v>78.227</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>76.554</v>
+        <v>-19.849</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>74.622</v>
+        <v>-21.217</v>
       </c>
     </row>
     <row r="34">
@@ -2870,10 +2778,10 @@
         <v>78.227</v>
       </c>
       <c r="R35" s="3" t="n">
-        <v>76.554</v>
+        <v>-19.849</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>74.622</v>
+        <v>-21.217</v>
       </c>
     </row>
     <row r="36">
@@ -2963,10 +2871,10 @@
         </is>
       </c>
       <c r="R36" s="3" t="n">
-        <v>57.19430104072499</v>
+        <v>-14.82939730591936</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>50.67467081361158</v>
+        <v>-14.40814358570391</v>
       </c>
     </row>
     <row r="37">
@@ -3233,59 +3141,95 @@
           <t>Money Market Investments</t>
         </is>
       </c>
-      <c r="B41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S41" s="3" t="n">
-        <v>0</v>
+      <c r="B41" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C41" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D41" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E41" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F41" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G41" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H41" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I41" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J41" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K41" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L41" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M41" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N41" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O41" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P41" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q41" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R41" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S41" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="42">
@@ -3743,15 +3687,11 @@
           <t xml:space="preserve">    Marketable Securities</t>
         </is>
       </c>
-      <c r="B47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>290.228</v>
@@ -3869,95 +3809,59 @@
           <t xml:space="preserve">    Accounts Receivable</t>
         </is>
       </c>
-      <c r="B49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3966,95 +3870,59 @@
           <t xml:space="preserve">    Notes Receivable</t>
         </is>
       </c>
-      <c r="B50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -4063,95 +3931,59 @@
           <t xml:space="preserve">    Loans Receivable</t>
         </is>
       </c>
-      <c r="B51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -4160,95 +3992,59 @@
           <t xml:space="preserve">    Other Current Receivables</t>
         </is>
       </c>
-      <c r="B52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -4257,95 +4053,59 @@
           <t xml:space="preserve">  Total Receivables</t>
         </is>
       </c>
-      <c r="B53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -4354,95 +4114,59 @@
           <t xml:space="preserve">    Inventories, Raw Materials &amp; Components</t>
         </is>
       </c>
-      <c r="B54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -4451,95 +4175,59 @@
           <t xml:space="preserve">    Inventories, Work In Process</t>
         </is>
       </c>
-      <c r="B55" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C55" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D55" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E55" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F55" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G55" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H55" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I55" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J55" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K55" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L55" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M55" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N55" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O55" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P55" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q55" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R55" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S55" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -4548,95 +4236,59 @@
           <t xml:space="preserve">    Inventories, Inventories Adjustments</t>
         </is>
       </c>
-      <c r="B56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -4645,95 +4297,59 @@
           <t xml:space="preserve">    Inventories, Finished Goods</t>
         </is>
       </c>
-      <c r="B57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -4742,95 +4358,59 @@
           <t xml:space="preserve">    Inventories, Other</t>
         </is>
       </c>
-      <c r="B58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -4839,95 +4419,59 @@
           <t xml:space="preserve">  Total Inventories</t>
         </is>
       </c>
-      <c r="B59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -4936,95 +4480,59 @@
           <t xml:space="preserve">  Other Current Assets</t>
         </is>
       </c>
-      <c r="B60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -5130,95 +4638,59 @@
           <t xml:space="preserve">  Investments And Advances</t>
         </is>
       </c>
-      <c r="B62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -5227,95 +4699,59 @@
           <t xml:space="preserve">      Land And Improvements</t>
         </is>
       </c>
-      <c r="B63" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C63" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D63" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E63" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F63" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G63" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H63" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I63" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J63" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K63" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L63" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M63" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N63" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O63" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P63" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q63" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R63" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S63" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -5324,95 +4760,59 @@
           <t xml:space="preserve">      Buildings And Improvements</t>
         </is>
       </c>
-      <c r="B64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -5421,95 +4821,59 @@
           <t xml:space="preserve">      Machinery, Furniture, Equipment</t>
         </is>
       </c>
-      <c r="B65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -5518,95 +4882,59 @@
           <t xml:space="preserve">      Construction In Progress</t>
         </is>
       </c>
-      <c r="B66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -5712,95 +5040,59 @@
           <t xml:space="preserve">    Gross Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -5809,95 +5101,59 @@
           <t xml:space="preserve">    Accumulated Depreciation</t>
         </is>
       </c>
-      <c r="B69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -5906,95 +5162,59 @@
           <t xml:space="preserve">  Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -6003,95 +5223,59 @@
           <t xml:space="preserve">  Intangible Assets</t>
         </is>
       </c>
-      <c r="B71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -6100,95 +5284,59 @@
           <t xml:space="preserve">    Goodwill</t>
         </is>
       </c>
-      <c r="B72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -6197,95 +5345,59 @@
           <t xml:space="preserve">  Other Long Term Assets</t>
         </is>
       </c>
-      <c r="B73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -6452,95 +5564,59 @@
           <t xml:space="preserve">    Accounts Payable</t>
         </is>
       </c>
-      <c r="B76" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C76" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D76" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E76" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F76" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G76" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H76" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I76" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J76" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K76" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L76" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M76" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N76" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O76" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P76" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q76" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R76" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S76" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B76" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C76" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N76" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q76" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S76" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -6549,95 +5625,59 @@
           <t xml:space="preserve">    Total Tax Payable</t>
         </is>
       </c>
-      <c r="B77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -6646,95 +5686,59 @@
           <t xml:space="preserve">    Other Current Payables</t>
         </is>
       </c>
-      <c r="B78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -6743,95 +5747,59 @@
           <t xml:space="preserve">    Current Accrued Expense</t>
         </is>
       </c>
-      <c r="B79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S79" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -6840,95 +5808,59 @@
           <t xml:space="preserve">  Accounts Payable &amp; Accrued Expense</t>
         </is>
       </c>
-      <c r="B80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B80" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C80" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q80" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R80" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S80" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -6937,66 +5869,44 @@
           <t xml:space="preserve">    Short-Term Debt</t>
         </is>
       </c>
-      <c r="B81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G81" s="3" t="n">
         <v>17.991</v>
       </c>
-      <c r="H81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M81" s="3" t="n">
         <v>5.053</v>
       </c>
-      <c r="N81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N81" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="O81" s="3" t="n">
         <v>57.34</v>
@@ -7020,95 +5930,59 @@
           <t xml:space="preserve">    Short-Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S82" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -7117,66 +5991,44 @@
           <t xml:space="preserve">  Short-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G83" s="3" t="n">
         <v>17.991</v>
       </c>
-      <c r="H83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M83" s="3" t="n">
         <v>5.053</v>
       </c>
-      <c r="N83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N83" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="O83" s="3" t="n">
         <v>57.34</v>
@@ -7200,95 +6052,59 @@
           <t xml:space="preserve">    Current Deferred Revenue</t>
         </is>
       </c>
-      <c r="B84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -7297,95 +6113,59 @@
           <t xml:space="preserve">    Current Deferred Taxes Liabilities</t>
         </is>
       </c>
-      <c r="B85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -7394,95 +6174,59 @@
           <t xml:space="preserve">  Deferred Tax And Revenue</t>
         </is>
       </c>
-      <c r="B86" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C86" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D86" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E86" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F86" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G86" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H86" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I86" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J86" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K86" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L86" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M86" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N86" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O86" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P86" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q86" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R86" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S86" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -7491,15 +6235,11 @@
           <t xml:space="preserve">  Other Current Liabilities</t>
         </is>
       </c>
-      <c r="B87" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C87" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C87" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D87" s="3" t="n">
         <v>2.248</v>
@@ -7507,75 +6247,47 @@
       <c r="E87" s="3" t="n">
         <v>5.728</v>
       </c>
-      <c r="F87" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G87" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H87" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I87" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J87" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K87" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L87" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M87" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N87" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O87" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P87" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q87" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R87" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S87" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -7677,95 +6389,59 @@
           <t xml:space="preserve">    Long-Term Debt</t>
         </is>
       </c>
-      <c r="B89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S89" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -7774,95 +6450,59 @@
           <t xml:space="preserve">    Long-Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B90" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C90" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D90" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E90" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F90" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G90" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H90" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I90" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J90" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K90" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L90" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M90" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N90" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O90" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P90" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q90" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R90" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S90" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B90" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C90" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D90" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P90" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q90" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R90" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S90" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -7871,95 +6511,59 @@
           <t xml:space="preserve">  Long-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -8209,95 +6813,59 @@
           <t>Other Liabilities for Banks</t>
         </is>
       </c>
-      <c r="B95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S95" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -8306,95 +6874,59 @@
           <t xml:space="preserve">  Pension And Retirement Benefit</t>
         </is>
       </c>
-      <c r="B96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -8403,95 +6935,59 @@
           <t xml:space="preserve">    NonCurrent Deferred Revenue</t>
         </is>
       </c>
-      <c r="B97" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C97" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D97" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E97" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F97" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G97" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H97" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I97" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J97" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K97" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L97" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M97" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N97" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O97" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P97" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q97" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R97" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S97" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -8500,15 +6996,11 @@
           <t xml:space="preserve">  NonCurrent Deferred Liabilities</t>
         </is>
       </c>
-      <c r="B98" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C98" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B98" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C98" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D98" s="3" t="n">
         <v>3.455</v>
@@ -8540,35 +7032,23 @@
       <c r="M98" s="3" t="n">
         <v>0.021</v>
       </c>
-      <c r="N98" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O98" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P98" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q98" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R98" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S98" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N98" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O98" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P98" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -8577,15 +7057,11 @@
           <t xml:space="preserve">  NonCurrent Deferred Income Tax</t>
         </is>
       </c>
-      <c r="B99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B99" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C99" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>3.455</v>
@@ -8617,35 +7093,23 @@
       <c r="M99" s="3" t="n">
         <v>0.021</v>
       </c>
-      <c r="N99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N99" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O99" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P99" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -8654,15 +7118,11 @@
           <t xml:space="preserve">  Other Long-Term Liabilities</t>
         </is>
       </c>
-      <c r="B100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C100" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D100" s="3" t="n">
         <v>368.048</v>
@@ -8670,75 +7130,47 @@
       <c r="E100" s="3" t="n">
         <v>427.693</v>
       </c>
-      <c r="F100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -8962,95 +7394,59 @@
           <t xml:space="preserve">  Preferred Stock</t>
         </is>
       </c>
-      <c r="B104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B104" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C104" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D104" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E104" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F104" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G104" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H104" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I104" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K104" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L104" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N104" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O104" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P104" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q104" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R104" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S104" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -9129,10 +7525,8 @@
       <c r="D106" s="3" t="n">
         <v>1.791</v>
       </c>
-      <c r="E106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E106" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F106" s="3" t="n">
         <v>2.281</v>
@@ -9155,20 +7549,14 @@
       <c r="L106" s="3" t="n">
         <v>2141.072</v>
       </c>
-      <c r="M106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M106" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N106" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O106" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="P106" s="3" t="n">
         <v>-0.176</v>
@@ -9250,95 +7638,59 @@
           <t xml:space="preserve">  Treasury Stock</t>
         </is>
       </c>
-      <c r="B108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S108" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -9408,95 +7760,59 @@
           <t xml:space="preserve">  Minority Interest</t>
         </is>
       </c>
-      <c r="B110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S110" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -66247,7 +64563,7 @@
       </c>
       <c r="D528" t="inlineStr">
         <is>
-          <t>NetInterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E528" t="inlineStr">
